--- a/Aksiyon_Mapping_Resimli.xlsx
+++ b/Aksiyon_Mapping_Resimli.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="1497">
   <si>
     <t>CSS Code</t>
   </si>
@@ -4495,6 +4495,21 @@
   </si>
   <si>
     <t>https://iis-akakce.akamaized.net/p.z?%2f%2fcdn.dsmcdn.com%2fty1569%2fprod%2fQC%2f20240925%2f08%2f931d0f9f-098d-3377-a9e1-bad706601700%2f1_org_zoom.jpg</t>
+  </si>
+  <si>
+    <t>Marka</t>
+  </si>
+  <si>
+    <t>Braun</t>
+  </si>
+  <si>
+    <t>Braun Saç</t>
+  </si>
+  <si>
+    <t>Revlon Saç</t>
+  </si>
+  <si>
+    <t>Oral-B</t>
   </si>
 </sst>
 </file>
@@ -4859,10 +4874,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4873,34 +4888,37 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -4911,22 +4929,25 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -4937,25 +4958,28 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -4966,31 +4990,34 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>36</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -5001,19 +5028,22 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>18</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -5024,34 +5054,37 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>49</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>50</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>51</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>52</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>53</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>18</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -5062,28 +5095,31 @@
         <v>57</v>
       </c>
       <c r="D7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E7" t="s">
         <v>58</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>62</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>18</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>64</v>
       </c>
@@ -5094,34 +5130,37 @@
         <v>66</v>
       </c>
       <c r="D8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E8" t="s">
         <v>67</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>68</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>69</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>70</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>71</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>72</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>73</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>18</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -5132,28 +5171,31 @@
         <v>77</v>
       </c>
       <c r="D9" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E9" t="s">
         <v>78</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>79</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>80</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>81</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>82</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>18</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -5164,22 +5206,25 @@
         <v>86</v>
       </c>
       <c r="D10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E10" t="s">
         <v>87</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>88</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>89</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>18</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -5190,34 +5235,37 @@
         <v>93</v>
       </c>
       <c r="D11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E11" t="s">
         <v>94</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>95</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>96</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>97</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>98</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>99</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>100</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>18</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -5228,19 +5276,22 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E12" t="s">
         <v>105</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>106</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>18</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -5251,31 +5302,34 @@
         <v>110</v>
       </c>
       <c r="D13" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E13" t="s">
         <v>111</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>112</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>113</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>114</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>115</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>116</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>18</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -5286,19 +5340,22 @@
         <v>120</v>
       </c>
       <c r="D14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E14" t="s">
         <v>121</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>122</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>18</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
@@ -5309,19 +5366,22 @@
         <v>126</v>
       </c>
       <c r="D15" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E15" t="s">
         <v>127</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>128</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>18</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -5332,19 +5392,22 @@
         <v>131</v>
       </c>
       <c r="D16" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E16" t="s">
         <v>132</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>133</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>18</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>135</v>
       </c>
@@ -5355,34 +5418,37 @@
         <v>137</v>
       </c>
       <c r="D17" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E17" t="s">
         <v>138</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>139</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>140</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>141</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>142</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>143</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>144</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>18</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -5393,22 +5459,25 @@
         <v>148</v>
       </c>
       <c r="D18" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E18" t="s">
         <v>149</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>150</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>151</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>18</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>153</v>
       </c>
@@ -5419,34 +5488,37 @@
         <v>155</v>
       </c>
       <c r="D19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E19" t="s">
         <v>156</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>157</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>158</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>159</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>160</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>161</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>162</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>18</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>164</v>
       </c>
@@ -5457,19 +5529,22 @@
         <v>166</v>
       </c>
       <c r="D20" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E20" t="s">
         <v>167</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>168</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>18</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -5480,28 +5555,31 @@
         <v>172</v>
       </c>
       <c r="D21" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E21" t="s">
         <v>173</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>174</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>175</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>176</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>177</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>178</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>180</v>
       </c>
@@ -5512,34 +5590,37 @@
         <v>182</v>
       </c>
       <c r="D22" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E22" t="s">
         <v>183</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>184</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>185</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>186</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>187</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>188</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>189</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>178</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>191</v>
       </c>
@@ -5550,34 +5631,37 @@
         <v>193</v>
       </c>
       <c r="D23" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E23" t="s">
         <v>194</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>195</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>196</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>197</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>198</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>199</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>200</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>178</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>202</v>
       </c>
@@ -5588,19 +5672,22 @@
         <v>204</v>
       </c>
       <c r="D24" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E24" t="s">
         <v>205</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>206</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>178</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>208</v>
       </c>
@@ -5611,28 +5698,31 @@
         <v>210</v>
       </c>
       <c r="D25" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E25" t="s">
         <v>211</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>212</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>213</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>214</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>215</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>178</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>217</v>
       </c>
@@ -5643,25 +5733,28 @@
         <v>219</v>
       </c>
       <c r="D26" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E26" t="s">
         <v>220</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>221</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>222</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>223</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>178</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>225</v>
       </c>
@@ -5672,22 +5765,25 @@
         <v>227</v>
       </c>
       <c r="D27" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E27" t="s">
         <v>228</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>229</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>230</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>178</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>232</v>
       </c>
@@ -5698,34 +5794,37 @@
         <v>234</v>
       </c>
       <c r="D28" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E28" t="s">
         <v>235</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>236</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>237</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>238</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>239</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>240</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>241</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>178</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>243</v>
       </c>
@@ -5736,25 +5835,28 @@
         <v>245</v>
       </c>
       <c r="D29" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E29" t="s">
         <v>246</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>247</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>248</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>249</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>178</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>251</v>
       </c>
@@ -5765,19 +5867,22 @@
         <v>253</v>
       </c>
       <c r="D30" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E30" t="s">
         <v>254</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>255</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>178</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>257</v>
       </c>
@@ -5785,19 +5890,22 @@
         <v>258</v>
       </c>
       <c r="D31" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E31" t="s">
         <v>259</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>260</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>178</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>262</v>
       </c>
@@ -5808,22 +5916,25 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E32" t="s">
         <v>265</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>266</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>267</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>178</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>269</v>
       </c>
@@ -5834,34 +5945,37 @@
         <v>271</v>
       </c>
       <c r="D33" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E33" t="s">
         <v>272</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>273</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>274</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>275</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>276</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>277</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>278</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>178</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>280</v>
       </c>
@@ -5869,19 +5983,22 @@
         <v>281</v>
       </c>
       <c r="D34" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E34" t="s">
         <v>282</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>283</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>178</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>285</v>
       </c>
@@ -5892,25 +6009,28 @@
         <v>287</v>
       </c>
       <c r="D35" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E35" t="s">
         <v>288</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>289</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>290</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>291</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>178</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>293</v>
       </c>
@@ -5921,28 +6041,31 @@
         <v>295</v>
       </c>
       <c r="D36" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E36" t="s">
         <v>296</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>297</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>298</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>299</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>300</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>178</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>302</v>
       </c>
@@ -5953,34 +6076,37 @@
         <v>304</v>
       </c>
       <c r="D37" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E37" t="s">
         <v>305</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>306</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>307</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>308</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>309</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>310</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>311</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>178</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>313</v>
       </c>
@@ -5991,25 +6117,28 @@
         <v>315</v>
       </c>
       <c r="D38" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E38" t="s">
         <v>316</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>317</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>318</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>319</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>178</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>321</v>
       </c>
@@ -6020,31 +6149,34 @@
         <v>323</v>
       </c>
       <c r="D39" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E39" t="s">
         <v>324</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>325</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>326</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>327</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>328</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>329</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" t="s">
         <v>178</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>331</v>
       </c>
@@ -6055,25 +6187,28 @@
         <v>333</v>
       </c>
       <c r="D40" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E40" t="s">
         <v>334</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>335</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>336</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>337</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>178</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>339</v>
       </c>
@@ -6084,34 +6219,37 @@
         <v>341</v>
       </c>
       <c r="D41" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E41" t="s">
         <v>342</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>343</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>344</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>345</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>346</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>347</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>348</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>178</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>350</v>
       </c>
@@ -6122,31 +6260,34 @@
         <v>352</v>
       </c>
       <c r="D42" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E42" t="s">
         <v>353</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>354</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>355</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>356</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>357</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>358</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
         <v>178</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>360</v>
       </c>
@@ -6157,28 +6298,31 @@
         <v>362</v>
       </c>
       <c r="D43" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E43" t="s">
         <v>363</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>364</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>365</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>366</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>367</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" t="s">
         <v>178</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>369</v>
       </c>
@@ -6189,34 +6333,37 @@
         <v>371</v>
       </c>
       <c r="D44" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E44" t="s">
         <v>372</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>373</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>374</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>375</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
         <v>376</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>377</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>378</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>178</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>379</v>
       </c>
@@ -6227,34 +6374,37 @@
         <v>381</v>
       </c>
       <c r="D45" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E45" t="s">
         <v>382</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>383</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>384</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>385</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>386</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>387</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>388</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>389</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M45" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>391</v>
       </c>
@@ -6265,31 +6415,34 @@
         <v>393</v>
       </c>
       <c r="D46" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E46" t="s">
         <v>394</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>395</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>396</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>397</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>398</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>399</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L46" t="s">
         <v>389</v>
       </c>
-      <c r="L46" t="s">
+      <c r="M46" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>401</v>
       </c>
@@ -6297,28 +6450,31 @@
         <v>402</v>
       </c>
       <c r="D47" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E47" t="s">
         <v>403</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>404</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>405</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>406</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>407</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" t="s">
         <v>389</v>
       </c>
-      <c r="L47" t="s">
+      <c r="M47" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>409</v>
       </c>
@@ -6326,25 +6482,28 @@
         <v>410</v>
       </c>
       <c r="D48" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E48" t="s">
         <v>411</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>412</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>413</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>414</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>389</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>416</v>
       </c>
@@ -6355,34 +6514,37 @@
         <v>418</v>
       </c>
       <c r="D49" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E49" t="s">
         <v>419</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>420</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>421</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>422</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>423</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>424</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>425</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>389</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M49" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>427</v>
       </c>
@@ -6393,31 +6555,34 @@
         <v>429</v>
       </c>
       <c r="D50" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E50" t="s">
         <v>430</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>431</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>432</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>433</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>434</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>435</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" t="s">
         <v>389</v>
       </c>
-      <c r="L50" t="s">
+      <c r="M50" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>437</v>
       </c>
@@ -6428,31 +6593,34 @@
         <v>439</v>
       </c>
       <c r="D51" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E51" t="s">
         <v>440</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>441</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>442</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>443</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>444</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>445</v>
       </c>
-      <c r="K51" t="s">
+      <c r="L51" t="s">
         <v>389</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M51" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>447</v>
       </c>
@@ -6463,19 +6631,22 @@
         <v>449</v>
       </c>
       <c r="D52" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E52" t="s">
         <v>450</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>451</v>
       </c>
-      <c r="K52" t="s">
+      <c r="L52" t="s">
         <v>389</v>
       </c>
-      <c r="L52" t="s">
+      <c r="M52" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>453</v>
       </c>
@@ -6486,31 +6657,34 @@
         <v>455</v>
       </c>
       <c r="D53" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E53" t="s">
         <v>456</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>457</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>458</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>459</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>460</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>461</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>389</v>
       </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>463</v>
       </c>
@@ -6521,25 +6695,28 @@
         <v>465</v>
       </c>
       <c r="D54" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E54" t="s">
         <v>466</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>467</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>468</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>469</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>389</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M54" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>471</v>
       </c>
@@ -6550,22 +6727,25 @@
         <v>473</v>
       </c>
       <c r="D55" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E55" t="s">
         <v>474</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>475</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>476</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>389</v>
       </c>
-      <c r="L55" t="s">
+      <c r="M55" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>478</v>
       </c>
@@ -6576,31 +6756,34 @@
         <v>480</v>
       </c>
       <c r="D56" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E56" t="s">
         <v>481</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>482</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>483</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>484</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>485</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>486</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" t="s">
         <v>389</v>
       </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>488</v>
       </c>
@@ -6611,25 +6794,28 @@
         <v>490</v>
       </c>
       <c r="D57" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E57" t="s">
         <v>491</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>492</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>493</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>494</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>389</v>
       </c>
-      <c r="L57" t="s">
+      <c r="M57" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>496</v>
       </c>
@@ -6640,22 +6826,25 @@
         <v>498</v>
       </c>
       <c r="D58" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E58" t="s">
         <v>499</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>500</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>501</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>389</v>
       </c>
-      <c r="L58" t="s">
+      <c r="M58" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>503</v>
       </c>
@@ -6666,22 +6855,25 @@
         <v>505</v>
       </c>
       <c r="D59" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E59" t="s">
         <v>506</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>507</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>508</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" t="s">
         <v>389</v>
       </c>
-      <c r="L59" t="s">
+      <c r="M59" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>510</v>
       </c>
@@ -6692,22 +6884,25 @@
         <v>512</v>
       </c>
       <c r="D60" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E60" t="s">
         <v>513</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>514</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>515</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>389</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>517</v>
       </c>
@@ -6718,25 +6913,28 @@
         <v>519</v>
       </c>
       <c r="D61" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E61" t="s">
         <v>520</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>521</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>522</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>523</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>389</v>
       </c>
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>525</v>
       </c>
@@ -6747,34 +6945,37 @@
         <v>527</v>
       </c>
       <c r="D62" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E62" t="s">
         <v>528</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>529</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>530</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>531</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
         <v>532</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>533</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>534</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>389</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>536</v>
       </c>
@@ -6785,34 +6986,37 @@
         <v>538</v>
       </c>
       <c r="D63" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E63" t="s">
         <v>539</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>540</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>541</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>542</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>543</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>544</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>545</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>546</v>
       </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>548</v>
       </c>
@@ -6823,31 +7027,34 @@
         <v>550</v>
       </c>
       <c r="D64" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E64" t="s">
         <v>551</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>552</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>553</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>554</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>555</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>556</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>546</v>
       </c>
-      <c r="L64" t="s">
+      <c r="M64" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>558</v>
       </c>
@@ -6858,34 +7065,37 @@
         <v>560</v>
       </c>
       <c r="D65" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E65" t="s">
         <v>561</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>562</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>563</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>564</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>565</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>566</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>567</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>546</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>569</v>
       </c>
@@ -6896,34 +7106,37 @@
         <v>571</v>
       </c>
       <c r="D66" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E66" t="s">
         <v>572</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>573</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>574</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>575</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>576</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>577</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>578</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" t="s">
         <v>546</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>580</v>
       </c>
@@ -6934,22 +7147,25 @@
         <v>582</v>
       </c>
       <c r="D67" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E67" t="s">
         <v>583</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>584</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>585</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>546</v>
       </c>
-      <c r="L67" t="s">
+      <c r="M67" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>587</v>
       </c>
@@ -6960,28 +7176,31 @@
         <v>589</v>
       </c>
       <c r="D68" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E68" t="s">
         <v>590</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>591</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>592</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>593</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>594</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>546</v>
       </c>
-      <c r="L68" t="s">
+      <c r="M68" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>596</v>
       </c>
@@ -6992,31 +7211,34 @@
         <v>598</v>
       </c>
       <c r="D69" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E69" t="s">
         <v>599</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>600</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>601</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>602</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>603</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>604</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
         <v>546</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>606</v>
       </c>
@@ -7027,22 +7249,25 @@
         <v>608</v>
       </c>
       <c r="D70" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E70" t="s">
         <v>609</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>610</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>611</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>546</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>613</v>
       </c>
@@ -7053,28 +7278,31 @@
         <v>615</v>
       </c>
       <c r="D71" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E71" t="s">
         <v>616</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>617</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>618</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>619</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>620</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>546</v>
       </c>
-      <c r="L71" t="s">
+      <c r="M71" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>622</v>
       </c>
@@ -7085,28 +7313,31 @@
         <v>624</v>
       </c>
       <c r="D72" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E72" t="s">
         <v>625</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>626</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>627</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>628</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>629</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>546</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>630</v>
       </c>
@@ -7117,34 +7348,37 @@
         <v>632</v>
       </c>
       <c r="D73" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E73" t="s">
         <v>633</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>634</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>635</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>636</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>637</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>638</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>639</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>546</v>
       </c>
-      <c r="L73" t="s">
+      <c r="M73" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>641</v>
       </c>
@@ -7155,34 +7389,37 @@
         <v>643</v>
       </c>
       <c r="D74" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E74" t="s">
         <v>644</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>645</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>646</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>647</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>648</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>649</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>650</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
         <v>546</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>652</v>
       </c>
@@ -7193,31 +7430,34 @@
         <v>654</v>
       </c>
       <c r="D75" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E75" t="s">
         <v>655</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>656</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>657</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>658</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>659</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>660</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>546</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>662</v>
       </c>
@@ -7228,31 +7468,34 @@
         <v>664</v>
       </c>
       <c r="D76" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E76" t="s">
         <v>665</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>666</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>667</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>668</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>669</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>670</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>546</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>672</v>
       </c>
@@ -7263,25 +7506,28 @@
         <v>674</v>
       </c>
       <c r="D77" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E77" t="s">
         <v>675</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>676</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>677</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>678</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>546</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>680</v>
       </c>
@@ -7292,34 +7538,37 @@
         <v>682</v>
       </c>
       <c r="D78" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E78" t="s">
         <v>683</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>684</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>685</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>686</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>687</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>688</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>689</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>546</v>
       </c>
-      <c r="L78" t="s">
+      <c r="M78" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>691</v>
       </c>
@@ -7330,34 +7579,37 @@
         <v>693</v>
       </c>
       <c r="D79" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E79" t="s">
         <v>694</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>695</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>696</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>697</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>698</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>699</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>700</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>546</v>
       </c>
-      <c r="L79" t="s">
+      <c r="M79" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>702</v>
       </c>
@@ -7368,28 +7620,31 @@
         <v>704</v>
       </c>
       <c r="D80" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E80" t="s">
         <v>705</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>706</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>707</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>708</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>709</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>546</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>711</v>
       </c>
@@ -7400,31 +7655,34 @@
         <v>713</v>
       </c>
       <c r="D81" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E81" t="s">
         <v>714</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>610</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>715</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>716</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>717</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>718</v>
       </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>546</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>720</v>
       </c>
@@ -7435,28 +7693,31 @@
         <v>722</v>
       </c>
       <c r="D82" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E82" t="s">
         <v>723</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>724</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>725</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>726</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>727</v>
       </c>
-      <c r="K82" t="s">
+      <c r="L82" t="s">
         <v>728</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>730</v>
       </c>
@@ -7467,25 +7728,28 @@
         <v>732</v>
       </c>
       <c r="D83" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E83" t="s">
         <v>733</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>734</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>735</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>736</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>728</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>738</v>
       </c>
@@ -7496,28 +7760,31 @@
         <v>740</v>
       </c>
       <c r="D84" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E84" t="s">
         <v>741</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>742</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>743</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>744</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>745</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>728</v>
       </c>
-      <c r="L84" t="s">
+      <c r="M84" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>747</v>
       </c>
@@ -7528,28 +7795,31 @@
         <v>749</v>
       </c>
       <c r="D85" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E85" t="s">
         <v>750</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>751</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>752</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>753</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
         <v>754</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>728</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>756</v>
       </c>
@@ -7560,28 +7830,31 @@
         <v>758</v>
       </c>
       <c r="D86" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E86" t="s">
         <v>759</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>760</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>761</v>
       </c>
-      <c r="H86" t="s">
+      <c r="I86" t="s">
         <v>762</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>763</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>728</v>
       </c>
-      <c r="L86" t="s">
+      <c r="M86" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>765</v>
       </c>
@@ -7589,19 +7862,22 @@
         <v>766</v>
       </c>
       <c r="D87" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E87" t="s">
         <v>767</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>768</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>728</v>
       </c>
-      <c r="L87" t="s">
+      <c r="M87" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>770</v>
       </c>
@@ -7612,31 +7888,34 @@
         <v>772</v>
       </c>
       <c r="D88" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E88" t="s">
         <v>773</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>774</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>775</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>776</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>777</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>778</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" t="s">
         <v>728</v>
       </c>
-      <c r="L88" t="s">
+      <c r="M88" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>780</v>
       </c>
@@ -7647,28 +7926,31 @@
         <v>782</v>
       </c>
       <c r="D89" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E89" t="s">
         <v>783</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>784</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>785</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>786</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>787</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" t="s">
         <v>728</v>
       </c>
-      <c r="L89" t="s">
+      <c r="M89" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>789</v>
       </c>
@@ -7679,31 +7961,34 @@
         <v>791</v>
       </c>
       <c r="D90" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E90" t="s">
         <v>792</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>793</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>794</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>795</v>
       </c>
-      <c r="H90" t="s">
+      <c r="I90" t="s">
         <v>796</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>797</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" t="s">
         <v>728</v>
       </c>
-      <c r="L90" t="s">
+      <c r="M90" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>798</v>
       </c>
@@ -7711,25 +7996,28 @@
         <v>799</v>
       </c>
       <c r="D91" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E91" t="s">
         <v>800</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>801</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>802</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>803</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" t="s">
         <v>728</v>
       </c>
-      <c r="L91" t="s">
+      <c r="M91" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>805</v>
       </c>
@@ -7740,25 +8028,28 @@
         <v>807</v>
       </c>
       <c r="D92" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E92" t="s">
         <v>808</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>809</v>
       </c>
-      <c r="H92" t="s">
+      <c r="I92" t="s">
         <v>810</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>811</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" t="s">
         <v>812</v>
       </c>
-      <c r="L92" t="s">
+      <c r="M92" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>814</v>
       </c>
@@ -7769,31 +8060,34 @@
         <v>816</v>
       </c>
       <c r="D93" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E93" t="s">
         <v>817</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>818</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>819</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>820</v>
       </c>
-      <c r="I93" t="s">
+      <c r="J93" t="s">
         <v>821</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>822</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" t="s">
         <v>812</v>
       </c>
-      <c r="L93" t="s">
+      <c r="M93" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>824</v>
       </c>
@@ -7804,31 +8098,34 @@
         <v>826</v>
       </c>
       <c r="D94" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E94" t="s">
         <v>827</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>828</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>829</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>830</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>831</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>832</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>833</v>
       </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>835</v>
       </c>
@@ -7839,31 +8136,34 @@
         <v>837</v>
       </c>
       <c r="D95" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E95" t="s">
         <v>838</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>839</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>840</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>841</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>842</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>843</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>833</v>
       </c>
-      <c r="L95" t="s">
+      <c r="M95" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>845</v>
       </c>
@@ -7874,22 +8174,25 @@
         <v>847</v>
       </c>
       <c r="D96" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E96" t="s">
         <v>848</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>849</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>850</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" t="s">
         <v>833</v>
       </c>
-      <c r="L96" t="s">
+      <c r="M96" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>852</v>
       </c>
@@ -7900,19 +8203,22 @@
         <v>854</v>
       </c>
       <c r="D97" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E97" t="s">
         <v>855</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>856</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" t="s">
         <v>833</v>
       </c>
-      <c r="L97" t="s">
+      <c r="M97" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>858</v>
       </c>
@@ -7923,19 +8229,22 @@
         <v>860</v>
       </c>
       <c r="D98" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E98" t="s">
         <v>861</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>862</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" t="s">
         <v>833</v>
       </c>
-      <c r="L98" t="s">
+      <c r="M98" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>864</v>
       </c>
@@ -7946,25 +8255,28 @@
         <v>866</v>
       </c>
       <c r="D99" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E99" t="s">
         <v>867</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>868</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>869</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>870</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>833</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>872</v>
       </c>
@@ -7975,19 +8287,22 @@
         <v>874</v>
       </c>
       <c r="D100" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E100" t="s">
         <v>875</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>876</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>833</v>
       </c>
-      <c r="L100" t="s">
+      <c r="M100" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>878</v>
       </c>
@@ -7998,28 +8313,31 @@
         <v>880</v>
       </c>
       <c r="D101" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E101" t="s">
         <v>881</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>882</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>883</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>884</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>885</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" t="s">
         <v>886</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>888</v>
       </c>
@@ -8030,22 +8348,25 @@
         <v>890</v>
       </c>
       <c r="D102" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E102" t="s">
         <v>891</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>892</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>893</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>886</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>895</v>
       </c>
@@ -8056,22 +8377,25 @@
         <v>897</v>
       </c>
       <c r="D103" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E103" t="s">
         <v>898</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>899</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>900</v>
       </c>
-      <c r="K103" t="s">
+      <c r="L103" t="s">
         <v>886</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>902</v>
       </c>
@@ -8082,22 +8406,25 @@
         <v>904</v>
       </c>
       <c r="D104" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E104" t="s">
         <v>905</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>906</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>907</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>886</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>909</v>
       </c>
@@ -8108,19 +8435,22 @@
         <v>911</v>
       </c>
       <c r="D105" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E105" t="s">
         <v>912</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>913</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>886</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>915</v>
       </c>
@@ -8131,28 +8461,31 @@
         <v>917</v>
       </c>
       <c r="D106" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E106" t="s">
         <v>918</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>919</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>920</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>921</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>922</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" t="s">
         <v>886</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>924</v>
       </c>
@@ -8163,19 +8496,22 @@
         <v>926</v>
       </c>
       <c r="D107" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E107" t="s">
         <v>927</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>928</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" t="s">
         <v>886</v>
       </c>
-      <c r="L107" t="s">
+      <c r="M107" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>930</v>
       </c>
@@ -8186,28 +8522,31 @@
         <v>932</v>
       </c>
       <c r="D108" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E108" t="s">
         <v>933</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>934</v>
       </c>
-      <c r="H108" t="s">
+      <c r="I108" t="s">
         <v>935</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>936</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>937</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" t="s">
         <v>886</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>939</v>
       </c>
@@ -8218,19 +8557,22 @@
         <v>941</v>
       </c>
       <c r="D109" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E109" t="s">
         <v>942</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>943</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>886</v>
       </c>
-      <c r="L109" t="s">
+      <c r="M109" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>945</v>
       </c>
@@ -8238,19 +8580,22 @@
         <v>946</v>
       </c>
       <c r="D110" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E110" t="s">
         <v>947</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>948</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" t="s">
         <v>833</v>
       </c>
-      <c r="L110" t="s">
+      <c r="M110" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>950</v>
       </c>
@@ -8258,25 +8603,28 @@
         <v>951</v>
       </c>
       <c r="D111" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E111" t="s">
         <v>952</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>953</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>954</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>955</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" t="s">
         <v>833</v>
       </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>957</v>
       </c>
@@ -8284,28 +8632,31 @@
         <v>958</v>
       </c>
       <c r="D112" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E112" t="s">
         <v>959</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>960</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>961</v>
       </c>
-      <c r="H112" t="s">
+      <c r="I112" t="s">
         <v>962</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>963</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" t="s">
         <v>833</v>
       </c>
-      <c r="L112" t="s">
+      <c r="M112" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>965</v>
       </c>
@@ -8313,28 +8664,31 @@
         <v>966</v>
       </c>
       <c r="D113" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E113" t="s">
         <v>967</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>968</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
         <v>962</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>963</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>969</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>833</v>
       </c>
-      <c r="L113" t="s">
+      <c r="M113" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>971</v>
       </c>
@@ -8342,28 +8696,31 @@
         <v>972</v>
       </c>
       <c r="D114" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E114" t="s">
         <v>973</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>974</v>
       </c>
-      <c r="H114" t="s">
+      <c r="I114" t="s">
         <v>975</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>976</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>977</v>
       </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>886</v>
       </c>
-      <c r="L114" t="s">
+      <c r="M114" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>979</v>
       </c>
@@ -8371,28 +8728,31 @@
         <v>980</v>
       </c>
       <c r="D115" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E115" t="s">
         <v>981</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>982</v>
       </c>
-      <c r="H115" t="s">
+      <c r="I115" t="s">
         <v>983</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>984</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>985</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>886</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>987</v>
       </c>
@@ -8400,19 +8760,22 @@
         <v>988</v>
       </c>
       <c r="D116" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E116" t="s">
         <v>989</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>990</v>
       </c>
-      <c r="K116" t="s">
+      <c r="L116" t="s">
         <v>886</v>
       </c>
-      <c r="L116" t="s">
+      <c r="M116" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>992</v>
       </c>
@@ -8420,31 +8783,34 @@
         <v>993</v>
       </c>
       <c r="D117" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E117" t="s">
         <v>994</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>995</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>996</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>997</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>998</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>999</v>
       </c>
-      <c r="K117" t="s">
+      <c r="L117" t="s">
         <v>812</v>
       </c>
-      <c r="L117" t="s">
+      <c r="M117" t="s">
         <v>1485</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1000</v>
       </c>
@@ -8452,31 +8818,34 @@
         <v>1001</v>
       </c>
       <c r="D118" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E118" t="s">
         <v>1002</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>1003</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>1004</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>1005</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>1006</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>1007</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>812</v>
       </c>
-      <c r="L118" t="s">
+      <c r="M118" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1009</v>
       </c>
@@ -8484,28 +8853,31 @@
         <v>1010</v>
       </c>
       <c r="D119" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E119" t="s">
         <v>1011</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>1012</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>1013</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>1014</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>1015</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" t="s">
         <v>812</v>
       </c>
-      <c r="L119" t="s">
+      <c r="M119" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1017</v>
       </c>
@@ -8513,28 +8885,31 @@
         <v>1018</v>
       </c>
       <c r="D120" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E120" t="s">
         <v>1019</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>1020</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
         <v>1021</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>1022</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>1023</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>812</v>
       </c>
-      <c r="L120" t="s">
+      <c r="M120" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1025</v>
       </c>
@@ -8542,25 +8917,28 @@
         <v>1026</v>
       </c>
       <c r="D121" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E121" t="s">
         <v>1027</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>1028</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
         <v>1029</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>1030</v>
       </c>
-      <c r="K121" t="s">
+      <c r="L121" t="s">
         <v>812</v>
       </c>
-      <c r="L121" t="s">
+      <c r="M121" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1032</v>
       </c>
@@ -8568,28 +8946,31 @@
         <v>1033</v>
       </c>
       <c r="D122" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E122" t="s">
         <v>1034</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>1035</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
         <v>1036</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>1037</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>1038</v>
       </c>
-      <c r="K122" t="s">
+      <c r="L122" t="s">
         <v>812</v>
       </c>
-      <c r="L122" t="s">
+      <c r="M122" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1040</v>
       </c>
@@ -8597,19 +8978,22 @@
         <v>1041</v>
       </c>
       <c r="D123" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E123" t="s">
         <v>1042</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>1043</v>
       </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>1044</v>
       </c>
-      <c r="L123" t="s">
+      <c r="M123" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1046</v>
       </c>
@@ -8617,19 +9001,22 @@
         <v>1047</v>
       </c>
       <c r="D124" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E124" t="s">
         <v>1048</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>1049</v>
       </c>
-      <c r="K124" t="s">
+      <c r="L124" t="s">
         <v>1044</v>
       </c>
-      <c r="L124" t="s">
+      <c r="M124" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1051</v>
       </c>
@@ -8637,19 +9024,22 @@
         <v>1052</v>
       </c>
       <c r="D125" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E125" t="s">
         <v>1053</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>1054</v>
       </c>
-      <c r="K125" t="s">
+      <c r="L125" t="s">
         <v>1044</v>
       </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>1055</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1056</v>
       </c>
@@ -8660,22 +9050,25 @@
         <v>1058</v>
       </c>
       <c r="D126" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E126" t="s">
         <v>1059</v>
       </c>
-      <c r="H126" t="s">
+      <c r="I126" t="s">
         <v>1060</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>1061</v>
       </c>
-      <c r="K126" t="s">
+      <c r="L126" t="s">
         <v>1062</v>
       </c>
-      <c r="L126" t="s">
+      <c r="M126" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1064</v>
       </c>
@@ -8686,25 +9079,28 @@
         <v>1066</v>
       </c>
       <c r="D127" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E127" t="s">
         <v>1067</v>
       </c>
-      <c r="H127" t="s">
+      <c r="I127" t="s">
         <v>1068</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>1069</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>1070</v>
       </c>
-      <c r="K127" t="s">
+      <c r="L127" t="s">
         <v>1062</v>
       </c>
-      <c r="L127" t="s">
+      <c r="M127" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1072</v>
       </c>
@@ -8715,22 +9111,25 @@
         <v>1074</v>
       </c>
       <c r="D128" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E128" t="s">
         <v>1075</v>
       </c>
-      <c r="H128" t="s">
+      <c r="I128" t="s">
         <v>1076</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>1077</v>
       </c>
-      <c r="K128" t="s">
+      <c r="L128" t="s">
         <v>1062</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1079</v>
       </c>
@@ -8741,25 +9140,28 @@
         <v>1081</v>
       </c>
       <c r="D129" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E129" t="s">
         <v>1082</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129" t="s">
         <v>1083</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>1084</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>1085</v>
       </c>
-      <c r="K129" t="s">
+      <c r="L129" t="s">
         <v>1062</v>
       </c>
-      <c r="L129" t="s">
+      <c r="M129" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1087</v>
       </c>
@@ -8770,22 +9172,25 @@
         <v>1089</v>
       </c>
       <c r="D130" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E130" t="s">
         <v>1090</v>
       </c>
-      <c r="H130" t="s">
+      <c r="I130" t="s">
         <v>1091</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>1092</v>
       </c>
-      <c r="K130" t="s">
+      <c r="L130" t="s">
         <v>1062</v>
       </c>
-      <c r="L130" t="s">
+      <c r="M130" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1094</v>
       </c>
@@ -8793,16 +9198,19 @@
         <v>1095</v>
       </c>
       <c r="D131" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E131" t="s">
         <v>1096</v>
       </c>
-      <c r="K131" t="s">
+      <c r="L131" t="s">
         <v>1062</v>
       </c>
-      <c r="L131" t="s">
+      <c r="M131" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1098</v>
       </c>
@@ -8813,25 +9221,28 @@
         <v>1100</v>
       </c>
       <c r="D132" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E132" t="s">
         <v>1101</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
         <v>1102</v>
       </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>1103</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
         <v>1104</v>
       </c>
-      <c r="K132" t="s">
+      <c r="L132" t="s">
         <v>1062</v>
       </c>
-      <c r="L132" t="s">
+      <c r="M132" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1106</v>
       </c>
@@ -8842,16 +9253,19 @@
         <v>1108</v>
       </c>
       <c r="D133" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E133" t="s">
         <v>1109</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" t="s">
         <v>1062</v>
       </c>
-      <c r="L133" t="s">
+      <c r="M133" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1111</v>
       </c>
@@ -8862,16 +9276,19 @@
         <v>1113</v>
       </c>
       <c r="D134" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E134" t="s">
         <v>1114</v>
       </c>
-      <c r="K134" t="s">
+      <c r="L134" t="s">
         <v>1062</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1116</v>
       </c>
@@ -8882,22 +9299,25 @@
         <v>1118</v>
       </c>
       <c r="D135" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E135" t="s">
         <v>1119</v>
       </c>
-      <c r="H135" t="s">
+      <c r="I135" t="s">
         <v>1120</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>1121</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" t="s">
         <v>1062</v>
       </c>
-      <c r="L135" t="s">
+      <c r="M135" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1123</v>
       </c>
@@ -8908,22 +9328,25 @@
         <v>1125</v>
       </c>
       <c r="D136" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E136" t="s">
         <v>1126</v>
       </c>
-      <c r="H136" t="s">
+      <c r="I136" t="s">
         <v>1127</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>1128</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" t="s">
         <v>1062</v>
       </c>
-      <c r="L136" t="s">
+      <c r="M136" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1130</v>
       </c>
@@ -8934,19 +9357,22 @@
         <v>1132</v>
       </c>
       <c r="D137" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E137" t="s">
         <v>1133</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" t="s">
         <v>1134</v>
       </c>
-      <c r="K137" t="s">
+      <c r="L137" t="s">
         <v>1062</v>
       </c>
-      <c r="L137" t="s">
+      <c r="M137" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1136</v>
       </c>
@@ -8957,19 +9383,22 @@
         <v>1138</v>
       </c>
       <c r="D138" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E138" t="s">
         <v>1139</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>1140</v>
       </c>
-      <c r="K138" t="s">
+      <c r="L138" t="s">
         <v>1062</v>
       </c>
-      <c r="L138" t="s">
+      <c r="M138" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1142</v>
       </c>
@@ -8980,25 +9409,28 @@
         <v>1144</v>
       </c>
       <c r="D139" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E139" t="s">
         <v>1145</v>
       </c>
-      <c r="H139" t="s">
+      <c r="I139" t="s">
         <v>1146</v>
       </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>1147</v>
       </c>
-      <c r="J139" t="s">
+      <c r="K139" t="s">
         <v>1148</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" t="s">
         <v>1062</v>
       </c>
-      <c r="L139" t="s">
+      <c r="M139" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1150</v>
       </c>
@@ -9009,25 +9441,28 @@
         <v>1152</v>
       </c>
       <c r="D140" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E140" t="s">
         <v>1153</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" t="s">
         <v>1154</v>
       </c>
-      <c r="I140" t="s">
+      <c r="J140" t="s">
         <v>1155</v>
       </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
         <v>1156</v>
       </c>
-      <c r="K140" t="s">
+      <c r="L140" t="s">
         <v>1062</v>
       </c>
-      <c r="L140" t="s">
+      <c r="M140" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1158</v>
       </c>
@@ -9038,25 +9473,28 @@
         <v>1160</v>
       </c>
       <c r="D141" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E141" t="s">
         <v>1161</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>1162</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>1163</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>1164</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" t="s">
         <v>1062</v>
       </c>
-      <c r="L141" t="s">
+      <c r="M141" t="s">
         <v>1165</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1166</v>
       </c>
@@ -9067,25 +9505,28 @@
         <v>1168</v>
       </c>
       <c r="D142" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E142" t="s">
         <v>1169</v>
       </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>1170</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>1171</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>1172</v>
       </c>
-      <c r="K142" t="s">
+      <c r="L142" t="s">
         <v>1062</v>
       </c>
-      <c r="L142" t="s">
+      <c r="M142" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1174</v>
       </c>
@@ -9096,16 +9537,19 @@
         <v>1176</v>
       </c>
       <c r="D143" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E143" t="s">
         <v>1177</v>
       </c>
-      <c r="K143" t="s">
+      <c r="L143" t="s">
         <v>1062</v>
       </c>
-      <c r="L143" t="s">
+      <c r="M143" t="s">
         <v>1178</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1179</v>
       </c>
@@ -9116,16 +9560,19 @@
         <v>1181</v>
       </c>
       <c r="D144" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E144" t="s">
         <v>1182</v>
       </c>
-      <c r="K144" t="s">
+      <c r="L144" t="s">
         <v>1062</v>
       </c>
-      <c r="L144" t="s">
+      <c r="M144" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1184</v>
       </c>
@@ -9133,16 +9580,19 @@
         <v>1185</v>
       </c>
       <c r="D145" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E145" t="s">
         <v>1186</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" t="s">
         <v>1062</v>
       </c>
-      <c r="L145" t="s">
+      <c r="M145" t="s">
         <v>1187</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1188</v>
       </c>
@@ -9153,16 +9603,19 @@
         <v>1190</v>
       </c>
       <c r="D146" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E146" t="s">
         <v>1191</v>
       </c>
-      <c r="K146" t="s">
+      <c r="L146" t="s">
         <v>1062</v>
       </c>
-      <c r="L146" t="s">
+      <c r="M146" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1193</v>
       </c>
@@ -9173,16 +9626,19 @@
         <v>1195</v>
       </c>
       <c r="D147" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E147" t="s">
         <v>1196</v>
       </c>
-      <c r="K147" t="s">
+      <c r="L147" t="s">
         <v>1062</v>
       </c>
-      <c r="L147" t="s">
+      <c r="M147" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1198</v>
       </c>
@@ -9193,25 +9649,28 @@
         <v>1200</v>
       </c>
       <c r="D148" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E148" t="s">
         <v>1201</v>
       </c>
-      <c r="H148" t="s">
+      <c r="I148" t="s">
         <v>1202</v>
       </c>
-      <c r="I148" t="s">
+      <c r="J148" t="s">
         <v>1203</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>1204</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" t="s">
         <v>1062</v>
       </c>
-      <c r="L148" t="s">
+      <c r="M148" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1206</v>
       </c>
@@ -9222,25 +9681,28 @@
         <v>1208</v>
       </c>
       <c r="D149" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E149" t="s">
         <v>1209</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>1210</v>
       </c>
-      <c r="I149" t="s">
+      <c r="J149" t="s">
         <v>1211</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>1212</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" t="s">
         <v>1062</v>
       </c>
-      <c r="L149" t="s">
+      <c r="M149" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1214</v>
       </c>
@@ -9251,25 +9713,28 @@
         <v>1216</v>
       </c>
       <c r="D150" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E150" t="s">
         <v>1217</v>
       </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>1218</v>
       </c>
-      <c r="I150" t="s">
+      <c r="J150" t="s">
         <v>1219</v>
       </c>
-      <c r="J150" t="s">
+      <c r="K150" t="s">
         <v>1220</v>
       </c>
-      <c r="K150" t="s">
+      <c r="L150" t="s">
         <v>1062</v>
       </c>
-      <c r="L150" t="s">
+      <c r="M150" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1222</v>
       </c>
@@ -9280,25 +9745,28 @@
         <v>1224</v>
       </c>
       <c r="D151" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E151" t="s">
         <v>1225</v>
       </c>
-      <c r="H151" t="s">
+      <c r="I151" t="s">
         <v>1226</v>
       </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>1227</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>1228</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" t="s">
         <v>1062</v>
       </c>
-      <c r="L151" t="s">
+      <c r="M151" t="s">
         <v>1229</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1230</v>
       </c>
@@ -9309,25 +9777,28 @@
         <v>1232</v>
       </c>
       <c r="D152" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E152" t="s">
         <v>1233</v>
       </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
         <v>1234</v>
       </c>
-      <c r="I152" t="s">
+      <c r="J152" t="s">
         <v>1235</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>1236</v>
       </c>
-      <c r="K152" t="s">
+      <c r="L152" t="s">
         <v>1062</v>
       </c>
-      <c r="L152" t="s">
+      <c r="M152" t="s">
         <v>1237</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1238</v>
       </c>
@@ -9335,16 +9806,19 @@
         <v>1239</v>
       </c>
       <c r="D153" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E153" t="s">
         <v>1240</v>
       </c>
-      <c r="K153" t="s">
+      <c r="L153" t="s">
         <v>1062</v>
       </c>
-      <c r="L153" t="s">
+      <c r="M153" t="s">
         <v>1241</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1242</v>
       </c>
@@ -9355,25 +9829,28 @@
         <v>1244</v>
       </c>
       <c r="D154" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E154" t="s">
         <v>1245</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>1246</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
         <v>1247</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>1248</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" t="s">
         <v>1062</v>
       </c>
-      <c r="L154" t="s">
+      <c r="M154" t="s">
         <v>1249</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1250</v>
       </c>
@@ -9384,25 +9861,28 @@
         <v>1252</v>
       </c>
       <c r="D155" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E155" t="s">
         <v>1253</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
         <v>1254</v>
       </c>
-      <c r="I155" t="s">
+      <c r="J155" t="s">
         <v>1255</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>1256</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" t="s">
         <v>1062</v>
       </c>
-      <c r="L155" t="s">
+      <c r="M155" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1258</v>
       </c>
@@ -9413,25 +9893,28 @@
         <v>1260</v>
       </c>
       <c r="D156" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E156" t="s">
         <v>1261</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>1262</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" t="s">
         <v>1263</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>1264</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" t="s">
         <v>1062</v>
       </c>
-      <c r="L156" t="s">
+      <c r="M156" t="s">
         <v>1265</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1266</v>
       </c>
@@ -9442,25 +9925,28 @@
         <v>1268</v>
       </c>
       <c r="D157" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E157" t="s">
         <v>1269</v>
       </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
         <v>1270</v>
       </c>
-      <c r="I157" t="s">
+      <c r="J157" t="s">
         <v>1271</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>1272</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" t="s">
         <v>1062</v>
       </c>
-      <c r="L157" t="s">
+      <c r="M157" t="s">
         <v>1273</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1274</v>
       </c>
@@ -9471,16 +9957,19 @@
         <v>1276</v>
       </c>
       <c r="D158" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E158" t="s">
         <v>1277</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" t="s">
         <v>1062</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M158" t="s">
         <v>1278</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1279</v>
       </c>
@@ -9488,16 +9977,19 @@
         <v>1280</v>
       </c>
       <c r="D159" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E159" t="s">
         <v>1281</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" t="s">
         <v>1062</v>
       </c>
-      <c r="L159" t="s">
+      <c r="M159" t="s">
         <v>1282</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1283</v>
       </c>
@@ -9508,16 +10000,19 @@
         <v>1285</v>
       </c>
       <c r="D160" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E160" t="s">
         <v>1286</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" t="s">
         <v>1062</v>
       </c>
-      <c r="L160" t="s">
+      <c r="M160" t="s">
         <v>1287</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1288</v>
       </c>
@@ -9525,19 +10020,22 @@
         <v>1289</v>
       </c>
       <c r="D161" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E161" t="s">
         <v>1290</v>
       </c>
-      <c r="H161" t="s">
+      <c r="I161" t="s">
         <v>1291</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" t="s">
         <v>1292</v>
       </c>
-      <c r="L161" t="s">
+      <c r="M161" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1294</v>
       </c>
@@ -9548,25 +10046,28 @@
         <v>1296</v>
       </c>
       <c r="D162" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E162" t="s">
         <v>1297</v>
       </c>
-      <c r="H162" t="s">
+      <c r="I162" t="s">
         <v>1298</v>
       </c>
-      <c r="I162" t="s">
+      <c r="J162" t="s">
         <v>1299</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>1300</v>
       </c>
-      <c r="K162" t="s">
+      <c r="L162" t="s">
         <v>1292</v>
       </c>
-      <c r="L162" t="s">
+      <c r="M162" t="s">
         <v>1301</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1302</v>
       </c>
@@ -9577,25 +10078,28 @@
         <v>1304</v>
       </c>
       <c r="D163" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E163" t="s">
         <v>1305</v>
       </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>1306</v>
       </c>
-      <c r="I163" t="s">
+      <c r="J163" t="s">
         <v>1307</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
         <v>1308</v>
       </c>
-      <c r="K163" t="s">
+      <c r="L163" t="s">
         <v>1292</v>
       </c>
-      <c r="L163" t="s">
+      <c r="M163" t="s">
         <v>1309</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1310</v>
       </c>
@@ -9606,25 +10110,28 @@
         <v>1312</v>
       </c>
       <c r="D164" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E164" t="s">
         <v>1313</v>
       </c>
-      <c r="H164" t="s">
+      <c r="I164" t="s">
         <v>1314</v>
       </c>
-      <c r="I164" t="s">
+      <c r="J164" t="s">
         <v>1315</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>1316</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" t="s">
         <v>1292</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1317</v>
       </c>
@@ -9635,22 +10142,25 @@
         <v>1319</v>
       </c>
       <c r="D165" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E165" t="s">
         <v>1320</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
         <v>1321</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>1322</v>
       </c>
-      <c r="K165" t="s">
+      <c r="L165" t="s">
         <v>1292</v>
       </c>
-      <c r="L165" t="s">
+      <c r="M165" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1324</v>
       </c>
@@ -9661,25 +10171,28 @@
         <v>1326</v>
       </c>
       <c r="D166" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E166" t="s">
         <v>1327</v>
       </c>
-      <c r="H166" t="s">
+      <c r="I166" t="s">
         <v>1328</v>
       </c>
-      <c r="I166" t="s">
+      <c r="J166" t="s">
         <v>1329</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>1330</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" t="s">
         <v>1292</v>
       </c>
-      <c r="L166" t="s">
+      <c r="M166" t="s">
         <v>1331</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1332</v>
       </c>
@@ -9690,25 +10203,28 @@
         <v>1334</v>
       </c>
       <c r="D167" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E167" t="s">
         <v>1335</v>
       </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
         <v>1336</v>
       </c>
-      <c r="I167" t="s">
+      <c r="J167" t="s">
         <v>1337</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>1338</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" t="s">
         <v>1292</v>
       </c>
-      <c r="L167" t="s">
+      <c r="M167" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1340</v>
       </c>
@@ -9719,25 +10235,28 @@
         <v>1342</v>
       </c>
       <c r="D168" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E168" t="s">
         <v>1343</v>
       </c>
-      <c r="H168" t="s">
+      <c r="I168" t="s">
         <v>1344</v>
       </c>
-      <c r="I168" t="s">
+      <c r="J168" t="s">
         <v>1345</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>1346</v>
       </c>
-      <c r="K168" t="s">
+      <c r="L168" t="s">
         <v>1292</v>
       </c>
-      <c r="L168" t="s">
+      <c r="M168" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1347</v>
       </c>
@@ -9748,19 +10267,22 @@
         <v>1349</v>
       </c>
       <c r="D169" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E169" t="s">
         <v>1350</v>
       </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
         <v>1351</v>
       </c>
-      <c r="K169" t="s">
+      <c r="L169" t="s">
         <v>1292</v>
       </c>
-      <c r="L169" t="s">
+      <c r="M169" t="s">
         <v>1352</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>1353</v>
       </c>
@@ -9771,25 +10293,28 @@
         <v>1355</v>
       </c>
       <c r="D170" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E170" t="s">
         <v>1356</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>1357</v>
       </c>
-      <c r="I170" t="s">
+      <c r="J170" t="s">
         <v>1358</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>1359</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" t="s">
         <v>1292</v>
       </c>
-      <c r="L170" t="s">
+      <c r="M170" t="s">
         <v>1360</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1361</v>
       </c>
@@ -9800,25 +10325,28 @@
         <v>1363</v>
       </c>
       <c r="D171" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E171" t="s">
         <v>1364</v>
       </c>
-      <c r="H171" t="s">
+      <c r="I171" t="s">
         <v>1365</v>
       </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>1366</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>1367</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" t="s">
         <v>1292</v>
       </c>
-      <c r="L171" t="s">
+      <c r="M171" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1369</v>
       </c>
@@ -9829,22 +10357,25 @@
         <v>1371</v>
       </c>
       <c r="D172" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E172" t="s">
         <v>1372</v>
       </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>1373</v>
       </c>
-      <c r="I172" t="s">
+      <c r="J172" t="s">
         <v>1374</v>
       </c>
-      <c r="K172" t="s">
+      <c r="L172" t="s">
         <v>1292</v>
       </c>
-      <c r="L172" t="s">
+      <c r="M172" t="s">
         <v>1375</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1361</v>
       </c>
@@ -9852,19 +10383,22 @@
         <v>1376</v>
       </c>
       <c r="D173" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E173" t="s">
         <v>1377</v>
       </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>1378</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" t="s">
         <v>1292</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1379</v>
       </c>
@@ -9872,22 +10406,25 @@
         <v>1380</v>
       </c>
       <c r="D174" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E174" t="s">
         <v>1381</v>
       </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>1382</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>1383</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" t="s">
         <v>1292</v>
       </c>
-      <c r="L174" t="s">
+      <c r="M174" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1385</v>
       </c>
@@ -9898,25 +10435,28 @@
         <v>1387</v>
       </c>
       <c r="D175" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E175" t="s">
         <v>1388</v>
       </c>
-      <c r="H175" t="s">
+      <c r="I175" t="s">
         <v>1389</v>
       </c>
-      <c r="I175" t="s">
+      <c r="J175" t="s">
         <v>1390</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>1391</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" t="s">
         <v>1292</v>
       </c>
-      <c r="L175" t="s">
+      <c r="M175" t="s">
         <v>1392</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>1393</v>
       </c>
@@ -9927,22 +10467,25 @@
         <v>1395</v>
       </c>
       <c r="D176" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E176" t="s">
         <v>1396</v>
       </c>
-      <c r="H176" t="s">
+      <c r="I176" t="s">
         <v>1397</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>1383</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" t="s">
         <v>1292</v>
       </c>
-      <c r="L176" t="s">
+      <c r="M176" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1399</v>
       </c>
@@ -9953,19 +10496,22 @@
         <v>1401</v>
       </c>
       <c r="D177" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E177" t="s">
         <v>1402</v>
       </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>1403</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" t="s">
         <v>1292</v>
       </c>
-      <c r="L177" t="s">
+      <c r="M177" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1405</v>
       </c>
@@ -9976,25 +10522,28 @@
         <v>1407</v>
       </c>
       <c r="D178" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E178" t="s">
         <v>1408</v>
       </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>1409</v>
       </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>1410</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>1411</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" t="s">
         <v>1292</v>
       </c>
-      <c r="L178" t="s">
+      <c r="M178" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1412</v>
       </c>
@@ -10005,22 +10554,25 @@
         <v>1414</v>
       </c>
       <c r="D179" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E179" t="s">
         <v>1415</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>1416</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>1417</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" t="s">
         <v>1292</v>
       </c>
-      <c r="L179" t="s">
+      <c r="M179" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1418</v>
       </c>
@@ -10031,22 +10583,25 @@
         <v>1420</v>
       </c>
       <c r="D180" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E180" t="s">
         <v>1421</v>
       </c>
-      <c r="I180" t="s">
+      <c r="J180" t="s">
         <v>1422</v>
       </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
         <v>1423</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" t="s">
         <v>1292</v>
       </c>
-      <c r="L180" t="s">
+      <c r="M180" t="s">
         <v>1424</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1425</v>
       </c>
@@ -10057,19 +10612,22 @@
         <v>1427</v>
       </c>
       <c r="D181" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E181" t="s">
         <v>1428</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>1429</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" t="s">
         <v>1292</v>
       </c>
-      <c r="L181" t="s">
+      <c r="M181" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1431</v>
       </c>
@@ -10080,16 +10638,19 @@
         <v>1433</v>
       </c>
       <c r="D182" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E182" t="s">
         <v>1434</v>
       </c>
-      <c r="K182" t="s">
+      <c r="L182" t="s">
         <v>1292</v>
       </c>
-      <c r="L182" t="s">
+      <c r="M182" t="s">
         <v>1435</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1436</v>
       </c>
@@ -10100,19 +10661,22 @@
         <v>1438</v>
       </c>
       <c r="D183" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E183" t="s">
         <v>1439</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>1440</v>
       </c>
-      <c r="K183" t="s">
+      <c r="L183" t="s">
         <v>1292</v>
       </c>
-      <c r="L183" t="s">
+      <c r="M183" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1441</v>
       </c>
@@ -10123,19 +10687,22 @@
         <v>1443</v>
       </c>
       <c r="D184" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E184" t="s">
         <v>1444</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>1445</v>
       </c>
-      <c r="K184" t="s">
+      <c r="L184" t="s">
         <v>1292</v>
       </c>
-      <c r="L184" t="s">
+      <c r="M184" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1447</v>
       </c>
@@ -10146,19 +10713,22 @@
         <v>1449</v>
       </c>
       <c r="D185" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E185" t="s">
         <v>1450</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>1451</v>
       </c>
-      <c r="K185" t="s">
+      <c r="L185" t="s">
         <v>1292</v>
       </c>
-      <c r="L185" t="s">
+      <c r="M185" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1452</v>
       </c>
@@ -10169,22 +10739,25 @@
         <v>1454</v>
       </c>
       <c r="D186" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E186" t="s">
         <v>1455</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>1456</v>
       </c>
-      <c r="J186" t="s">
+      <c r="K186" t="s">
         <v>1457</v>
       </c>
-      <c r="K186" t="s">
+      <c r="L186" t="s">
         <v>1292</v>
       </c>
-      <c r="L186" t="s">
+      <c r="M186" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1459</v>
       </c>
@@ -10192,19 +10765,22 @@
         <v>1460</v>
       </c>
       <c r="D187" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E187" t="s">
         <v>1461</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>1462</v>
       </c>
-      <c r="K187" t="s">
+      <c r="L187" t="s">
         <v>1292</v>
       </c>
-      <c r="L187" t="s">
+      <c r="M187" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1464</v>
       </c>
@@ -10215,16 +10791,19 @@
         <v>1466</v>
       </c>
       <c r="D188" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E188" t="s">
         <v>1467</v>
       </c>
-      <c r="K188" t="s">
+      <c r="L188" t="s">
         <v>1292</v>
       </c>
-      <c r="L188" t="s">
+      <c r="M188" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1469</v>
       </c>
@@ -10235,16 +10814,19 @@
         <v>1470</v>
       </c>
       <c r="D189" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E189" t="s">
         <v>1471</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" t="s">
         <v>1292</v>
       </c>
-      <c r="L189" t="s">
+      <c r="M189" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1473</v>
       </c>
@@ -10252,16 +10834,19 @@
         <v>1474</v>
       </c>
       <c r="D190" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E190" t="s">
         <v>1475</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" t="s">
         <v>1292</v>
       </c>
-      <c r="L190" t="s">
+      <c r="M190" t="s">
         <v>1476</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1477</v>
       </c>
@@ -10269,12 +10854,15 @@
         <v>1478</v>
       </c>
       <c r="D191" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E191" t="s">
         <v>1479</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" t="s">
         <v>1292</v>
       </c>
-      <c r="L191" t="s">
+      <c r="M191" t="s">
         <v>1480</v>
       </c>
     </row>

--- a/Aksiyon_Mapping_Resimli.xlsx
+++ b/Aksiyon_Mapping_Resimli.xlsx
@@ -8028,7 +8028,7 @@
         <v>807</v>
       </c>
       <c r="D92" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E92" t="s">
         <v>808</v>
@@ -8060,7 +8060,7 @@
         <v>816</v>
       </c>
       <c r="D93" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E93" t="s">
         <v>817</v>
